--- a/รายได้พันธมิตรUFA66.xlsx
+++ b/รายได้พันธมิตรUFA66.xlsx
@@ -2275,7 +2275,7 @@
     <t>-47627</t>
   </si>
   <si>
-    <t>10817</t>
+    <t>10818</t>
   </si>
   <si>
     <t>ufrcbka7</t>

--- a/รายได้พันธมิตรUFA66.xlsx
+++ b/รายได้พันธมิตรUFA66.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="รายได้พันธมิตร UFA66" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -2275,7 +2275,7 @@
     <t>-47627</t>
   </si>
   <si>
-    <t>10818</t>
+    <t>6818</t>
   </si>
   <si>
     <t>ufrcbka7</t>

--- a/รายได้พันธมิตรUFA66.xlsx
+++ b/รายได้พันธมิตรUFA66.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="937">
   <si>
     <t>ยูส</t>
   </si>
@@ -2759,6 +2759,69 @@
   </si>
   <si>
     <t>37</t>
+  </si>
+  <si>
+    <t>ufrcbya4</t>
+  </si>
+  <si>
+    <t>-10</t>
+  </si>
+  <si>
+    <t>ufrcbza1</t>
+  </si>
+  <si>
+    <t>3347</t>
+  </si>
+  <si>
+    <t>-6616</t>
+  </si>
+  <si>
+    <t>-3269</t>
+  </si>
+  <si>
+    <t>ufrcbza9</t>
+  </si>
+  <si>
+    <t>-677</t>
+  </si>
+  <si>
+    <t>-699</t>
+  </si>
+  <si>
+    <t>ufrcbzb1</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>-506</t>
+  </si>
+  <si>
+    <t>-258</t>
+  </si>
+  <si>
+    <t>ufrcbzb2</t>
+  </si>
+  <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>264</t>
+  </si>
+  <si>
+    <t>ufrcbzb3</t>
+  </si>
+  <si>
+    <t>529</t>
+  </si>
+  <si>
+    <t>17573</t>
+  </si>
+  <si>
+    <t>-7411</t>
+  </si>
+  <si>
+    <t>10162</t>
   </si>
 </sst>
 </file>
@@ -2798,7 +2861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J252"/>
+  <dimension ref="A1:J258"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -10865,6 +10928,198 @@
         <v>915</v>
       </c>
     </row>
+    <row r="253" spans="1:10">
+      <c r="A253" s="0" t="s">
+        <v>916</v>
+      </c>
+      <c r="B253" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C253" s="0" t="s">
+        <v>372</v>
+      </c>
+      <c r="D253" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E253" s="0" t="s">
+        <v>917</v>
+      </c>
+      <c r="F253" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="G253" s="0" t="s">
+        <v>372</v>
+      </c>
+      <c r="H253" s="0" t="s">
+        <v>917</v>
+      </c>
+      <c r="I253" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="J253" s="0" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10">
+      <c r="A254" s="0" t="s">
+        <v>918</v>
+      </c>
+      <c r="B254" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C254" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D254" s="0" t="s">
+        <v>919</v>
+      </c>
+      <c r="E254" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F254" s="0" t="s">
+        <v>920</v>
+      </c>
+      <c r="G254" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="H254" s="0" t="s">
+        <v>921</v>
+      </c>
+      <c r="I254" s="0" t="s">
+        <v>557</v>
+      </c>
+      <c r="J254" s="0" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10">
+      <c r="A255" s="0" t="s">
+        <v>922</v>
+      </c>
+      <c r="B255" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C255" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="D255" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E255" s="0" t="s">
+        <v>923</v>
+      </c>
+      <c r="F255" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="G255" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="H255" s="0" t="s">
+        <v>924</v>
+      </c>
+      <c r="I255" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="J255" s="0" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10">
+      <c r="A256" s="0" t="s">
+        <v>925</v>
+      </c>
+      <c r="B256" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C256" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D256" s="0" t="s">
+        <v>926</v>
+      </c>
+      <c r="E256" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F256" s="0" t="s">
+        <v>927</v>
+      </c>
+      <c r="G256" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="H256" s="0" t="s">
+        <v>928</v>
+      </c>
+      <c r="I256" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="J256" s="0" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10">
+      <c r="A257" s="0" t="s">
+        <v>929</v>
+      </c>
+      <c r="B257" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C257" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="D257" s="0" t="s">
+        <v>930</v>
+      </c>
+      <c r="E257" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F257" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="G257" s="0" t="s">
+        <v>931</v>
+      </c>
+      <c r="H257" s="0" t="s">
+        <v>930</v>
+      </c>
+      <c r="I257" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="J257" s="0" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10">
+      <c r="A258" s="0" t="s">
+        <v>932</v>
+      </c>
+      <c r="B258" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C258" s="0" t="s">
+        <v>933</v>
+      </c>
+      <c r="D258" s="0" t="s">
+        <v>934</v>
+      </c>
+      <c r="E258" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F258" s="0" t="s">
+        <v>935</v>
+      </c>
+      <c r="G258" s="0" t="s">
+        <v>767</v>
+      </c>
+      <c r="H258" s="0" t="s">
+        <v>936</v>
+      </c>
+      <c r="I258" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="J258" s="0" t="s">
+        <v>767</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
